--- a/accrued-commissions-analysis/Accrued_Commissions_Unclaimed_Property_Analysis.xlsx
+++ b/accrued-commissions-analysis/Accrued_Commissions_Unclaimed_Property_Analysis.xlsx
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="736">
   <si>
     <t xml:space="preserve">Accrued Commissions - Unclaimed Property Exposure by Entity</t>
   </si>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">Current-month accrued (column D) is all September/October 2026 deposits in normal matching workflow. It is included so the total ties to the cash-requirements Summary, but none of it is near any dormancy period.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nothing here is legal advice. Dormancy periods, report dates and due-diligence rules on the State Rules tab were sourced from statute summaries and state guidance found by web search; the statute pages themselves could not be opened from this session. Have counsel or your unclaimed-property advisor confirm before filing.</t>
+    <t xml:space="preserve">Nothing here is legal advice. Dormancy periods, report dates, due-diligence rules, VDA terms and anti-limitation provisions on the State Rules tab were verified against the statute text and state treasury pages on 10/6/2026 (URLs in the Sources column). They state the rules; applying them to independent-contractor commissions and to the ICA forfeiture clauses is a judgment for counsel to confirm before filing.</t>
   </si>
   <si>
     <t xml:space="preserve">Unbooked deposited checks - item detail (prior-month accrued commissions block of each entity tab)</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">RESOLVED: agents are independent contractors</t>
   </si>
   <si>
-    <t xml:space="preserve">User confirmed 10/6/2026. Texas' 1-year rule applies to 'wages' as defined in Labor Code 61.001, which excludes independent contractors, so the 3-year general rule is the likely Texas test. Illinois and Alabama reach 'other compensation for personal services' and Pennsylvania lists commissions, so their shorter periods likely apply. Florida's wage rule is not shown to reach contractors, so 5 years is likely. Counsel should confirm each.</t>
+    <t xml:space="preserve">User confirmed 10/6/2026. Verified 10/6/2026 from the statute text: Texas' 1-year rule applies to 'wages' as defined in Labor Code 61.001, which excludes independent contractors, and the Comptroller's property-code table puts commissions (MS02) at 3 years, so the 3-year general rule is the Texas test. Illinois, Pennsylvania and Alabama each reach 'other compensation for personal services', so their shorter periods apply. Florida's wage rule is not shown to reach contractors, so 5 years is likely. Counsel should confirm each.</t>
   </si>
   <si>
     <t xml:space="preserve">Confirm with counsel.</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">ICA CLAUSES THAT REDUCE WHAT IS OWED TO AGENTS - legal question</t>
   </si>
   <si>
-    <t xml:space="preserve">Every ICA lets the Broker hold or apply commissions against amounts the agent owes (dues, fees, E&amp;O deductibles, indemnity) and conditions post-termination payouts on dues being paid in full. The Philly ICA goes further: an incomplete file 30 days past closing is paid 50/50 and 60 days past closing is 'forfeited'; a license not reactivated within 30 days means 'brokerage will keep 100% of commission'. TUR's agreement forfeits accrued commissions if the agent collects in their own name or breaches Section 5. A documented offset reduces the agent's share dollar for dollar. A contractual forfeiture is less certain: Alabama's act (and, per secondary sources, most states' acts) says a contractual limitation on the owner's right does not prevent property from being presumed abandoned. Whether Texas, Pennsylvania, Illinois or Florida would honor these clauses against an escheat claim is for counsel. Do not treat a forfeiture as the company's money until counsel says so AND the triggering facts (closing date, file status at day 60, termination date) are documented per item. See the ICA Terms tab.</t>
+    <t xml:space="preserve">Every ICA lets the Broker hold or apply commissions against amounts the agent owes (dues, fees, E&amp;O deductibles, indemnity) and conditions post-termination payouts on dues being paid in full. The Philly ICA goes further: an incomplete file 30 days past closing is paid 50/50 and 60 days past closing is 'forfeited'; a license not reactivated within 30 days means 'brokerage will keep 100% of commission'. TUR's agreement forfeits accrued commissions if the agent collects in their own name or breaches Section 5. A documented offset reduces the agent's share dollar for dollar. A contractual forfeiture is less certain. Verified 10/6/2026: Texas (Prop. Code 74.308), Illinois (765 ILCS 1026/15-610(a)), Florida (717.129(1)) and Alabama (35-12-88(a)) each say that the expiration of a period specified by CONTRACT does not prevent property from being presumed abandoned, and Texas 74.309 separately bars taking funds into income by private agreement to circumvent the unclaimed property process. Pennsylvania's 1301.16 mentions only statute and court order, not contract, and has no private-escheat section, so the Philly clause is a contract-law question there; but most Philly items default to Texas, where 74.308-74.309 apply. Whether any state would honor these clauses against an escheat claim is for counsel. Do not treat a forfeiture as the company's money until counsel says so AND the triggering facts (closing date, file status at day 60, termination date) are documented per item. See the ICA Terms tab.</t>
   </si>
   <si>
     <t xml:space="preserve">Counsel; Accounting to document per item.</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">ACTION: run due-diligence letters before any filing</t>
   </si>
   <si>
-    <t xml:space="preserve">Every state in scope requires a written notice to the owner before remittance (TX: &gt;$250, 60+ days before delivery; PA/IL/FL/AL/MO: $50 threshold per sources). A response from the owner stops the clock and lets you pay them directly instead of the state.</t>
+    <t xml:space="preserve">Every state in scope requires a written notice to the owner before remittance (verified 10/6/2026 - TX: more than $250, at least 60 days before delivery, mail or e-mail, Prop. Code 74.1011; PA: $50 or more, 60-120 days before April 15, 72 P.S. 1301.10a; IL: $50 or more, 60 days to one year before filing, 765 ILCS 1026/15-501; FL: $50 or more, 60-120 days before filing with the statutory heading, 717.117(6)-(7); AL: $50 or more, at least 60 days before filing, 35-12-76(d)). A response from the owner stops the clock and lets you pay them directly instead of the state.</t>
   </si>
   <si>
     <t xml:space="preserve">Accounting; template letters.</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">ACTION: consider a Voluntary Disclosure Agreement for Texas</t>
   </si>
   <si>
-    <t xml:space="preserve">Three Texas entities hold about 85% of the aged balance. Texas waives penalty and interest under a VDA but it must be requested before any Comptroller inquiry. Florida has a similar program. Confirm eligibility with the Comptroller or counsel.</t>
+    <t xml:space="preserve">Three Texas entities hold about 85% of the aged balance. Texas waives penalty and interest under Prop. Code 74.707; the request goes to UP.VDA.requests@cpa.texas.gov with the company name, FEIN, contact, estimated remittance and any audit-contact date, and the look-back is 10 years (Pub. 96-576). Pennsylvania, Illinois, Florida and Alabama each run a VDA program with penalty and interest waived (State Rules col K; Florida's is open only to holders that have never filed). Verified 10/6/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">ACTION: items that are not the company's money</t>
@@ -1760,10 +1760,10 @@
     <t xml:space="preserve">Counsel.</t>
   </si>
   <si>
-    <t xml:space="preserve">NOT VERIFIED in this session</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statute and state-treasury web pages were blocked by this session's network policy, so every rule on the State Rules tab rests on search-engine summaries of those pages and on secondary sources (Sovos, UPPO, law-firm alerts). Specific items I could not confirm: Illinois business-holder report deadline; PA December 31 cutoff and VDA terms; FL and AL due-diligence thresholds; MO VDA. Treat the State Rules tab as a starting point for counsel, not a filing position.</t>
+    <t xml:space="preserve">VERIFIED 10/6/2026 - and what is still open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every rule on the State Rules tab for TX, IL, PA, FL and AL (periods, section numbers, report cutoff and due date, due-diligence threshold and timing, VDA terms, anti-limitation provision) was read from the statute text and the state treasury pages on 10/6/2026; the URLs are in the Sources column. Corrections made: IL business holders file by May 1 for the calendar year (not November 1 / June 30); FL's operative long period for a Florida holder with an unknown owner address is 3 years under 717.1035 (not 5); the PA commissions rule is 1301.10(2) (not 1301.5); PA, FL and TX VDA descriptions replaced with the treasury pages' own terms. STILL OPEN: (1) no court decision or Comptroller ruling specifically on broker-to-agent commissions was found - the Texas 3-year position rests on the statutory definitions and the Comptroller's MS02 table; (2) whether a court would enforce the Philly ICA 60-day forfeiture against an escheat claim (the PA statute is silent on contract-based bars; TX 74.308-74.309 cut against it); (3) deposit date is a proxy for the payable date; (4) Missouri and DC not researched (no holder formed there, DC balance $0); (5) Texas VDA eligibility for an entity that has filed before is not stated on the Comptroller pages - ask when requesting.</t>
   </si>
   <si>
     <t xml:space="preserve">Counsel / unclaimed-property advisor.</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">7. Classification hints are heuristics on amount and memo text only; they are not conclusions.</t>
   </si>
   <si>
-    <t xml:space="preserve">8. State rules were researched by web search on 10/6/2026. Primary statute pages could not be opened from this session; see the State Rules tab 'Verification status' column for what is and is not confirmed.</t>
+    <t xml:space="preserve">8. State rules were first drafted from web-search summaries on 10/6/2026 and then verified the same day against the statute text (statutes.capitol.texas.gov, ilga.gov, PA Treasury's reprint of 72 P.S. 1301.1 et seq., flsenate.gov, Alabama Treasury's reprint of Ala. Code 35-12-70 et seq.) and each state's holder-reporting pages. The State Rules tab 'Verification status' column records what was read and the Sources column the URLs.</t>
   </si>
   <si>
     <t xml:space="preserve">9. Three fee documents were also provided 10/6/2026 (ICA Fee Structure Cheat Sheet xlsx, a scanned PDF of the same sheet, and the JV ICA Transaction Fee Summary docx with the older $495/$895 schedule); their amounts are in Summary rows 4-7.</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">Unclaimed property rules by state - dormancy periods applied in this analysis</t>
   </si>
   <si>
-    <t xml:space="preserve">Short period = the period for wages / compensation for personal services. Long period = the general catch-all period. Which one applies to independent-contractor agent commissions is a legal question that differs by state (see basis columns). Verification column says what could and could not be confirmed from primary sources in this session.</t>
+    <t xml:space="preserve">Short period = the period for wages / compensation for personal services. Long period = the general catch-all period. Which one applies to independent-contractor agent commissions is a legal question that differs by state (see basis columns). Verification column records what was confirmed from the statute text and state treasury pages on 10/6/2026, including each state's anti-limitation provision; Sources lists the URLs actually read.</t>
   </si>
   <si>
     <t xml:space="preserve">State</t>
@@ -2126,154 +2126,157 @@
     <t xml:space="preserve">Texas</t>
   </si>
   <si>
-    <t xml:space="preserve">Unclaimed 'wages' - Tex. Prop. Code 72.1015 (1 year). 'Wages' takes its meaning from Labor Code 61.001, which covers compensation owed by an EMPLOYER to an EMPLOYEE and excludes independent contractors. Independent-contractor agent commissions therefore likely fall under the general rule, not the 1-year rule - confirm with counsel / Comptroller.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">General personal property - Tex. Prop. Code 72.101(a): presumed abandoned after more than 3 years with owner location unknown and no claim/act of ownership.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">July 1 (Tex. Prop. Code 74.101)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">March 1 (property held on March 1 is reported the following July 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notice to owner by mail/e-mail at least 60 days before delivery for property over $250 (Tex. Prop. Code 74.1011).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comptroller offers a Voluntary Disclosure Agreement with waiver of penalty and interest; not available once an investigation has started or (per secondary sources) to holders who have filed Texas reports before.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormancy periods, report date, and due-diligence rule confirmed from search summaries of the statute text; statute pages themselves were blocked by this session's network policy. No business-to-business exemption was found for Texas.</t>
+    <t xml:space="preserve">Unclaimed wages - Tex. Prop. Code 72.1015: 'wages' has the meaning assigned by Labor Code 61.001 and is presumed abandoned after more than 1 year. Labor Code 61.001(7) defines wages as compensation owed by an EMPLOYER for labor or services rendered by an EMPLOYEE (whether computed on a time, task, piece, commission or other basis), and 61.001(3)(B) says 'employee' does not include an independent contractor. Independent-contractor agent commissions are therefore outside 72.1015. The Comptroller's reporting manual (Pub. 96-478, revised March 2026) lists property code MS01 'Wages, payroll or salary' at 1 year and MS02 'Commissions' at 3 years.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General rule - Tex. Prop. Code 72.101(a): personal property is presumed abandoned if, for longer than 3 years, the owner's location is unknown to the holder and no claim has been asserted or act of ownership exercised. Comptroller property code MS02 'Commissions' = 3 years (Pub. 96-478).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">July 1 (74.101(a): a holder who on March 1 holds reportable property files on or before the following July 1; 74.301(a): the property is delivered with the report)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">March 1 (74.101). Comptroller deadline table for report year 2026: 3-year property with last contact 3/02/2022 - 3/01/2023 is due 7/1/2026; 1-year property with last contact 3/02/2024 - 3/01/2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1011(a): a holder who on March 1 holds property valued at more than $250 must, not later than the 60th day before delivery to the Comptroller, send written notice by mail to the owner's last known address or by e-mail; not required where the holder has no physical or e-mail address on record (74.1011(b)(2)); postage may be charged against the property (74.1011(c)).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.707(a)-(b): the Comptroller may waive penalty or interest where the holder made a good-faith effort to comply, and may set periods for reporting delinquent property without penalty or interest. Comptroller VDA page (claimittexas.gov/app/disclosure-program): written request by e-mail to UP.VDA.requests@cpa.texas.gov with company name, contact, FEIN, address, estimated remittance and the date of any audit contact. Pub. 96-576 (08/2026): the unclaimed-property VDA look-back is 10 years. Without a VDA: penalty 5% of the value, plus a further 5% if more than 30 days late (74.706); interest 10% per year from the due date (74.705). Nothing on the Comptroller pages limits VDAs to first-time filers; the prior draft's statement to that effect came from a secondary source and is withdrawn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED from the statute text on 10/6/2026: Prop. Code 72.101, 72.1015, 74.101, 74.1011, 74.301, 74.308, 74.309, 74.705-74.707 and Labor Code 61.001 read at statutes.capitol.texas.gov; Comptroller Pub. 96-478 (rev. March 2026) property-code table, Reporting Deadlines page, VDA page and Pub. 96-576 read. ANTI-LIMITATION: 74.308 - expiration of any period specified by CONTRACT, statute or court order during which a claim may be brought does not prevent property from being presumed abandoned or affect the duty to report and deliver. 74.309 - private escheat prohibited: no business may act through private agreement or any other means to take or divert funds into income for the purpose of circumventing the unclaimed property process. No business-to-business exemption exists in chapters 72-74.</t>
   </si>
   <si>
     <t xml:space="preserve">LONG</t>
   </si>
   <si>
-    <t xml:space="preserve">Agents are independent contractors (confirmed by user). Texas' 1-year rule covers 'wages' as defined in Labor Code 61.001, which is limited to employer-to-employee compensation and expressly excludes independent contractors. The 3-year general rule is therefore the likely test. Confirm with counsel; some advisors report commissions under NAUPA code MS02 conservatively on the shorter period.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://statutes.capitol.texas.gov/docs/PR/htm/PR.72.htm ; https://statutes.capitol.texas.gov/Docs/PR/htm/PR.74.htm ; https://texas.public.law/statutes/tex._prop._code_section_72.1015 ; https://texas.public.law/statutes/tex._labor_code_section_61.001 ; https://www.comptroller.texas.gov/taxes/publications/96-576.php</t>
+    <t xml:space="preserve">Agents are independent contractors (confirmed by user). 72.1015 reaches only 'wages' as defined in Labor Code 61.001(7): compensation owed by an employer to an employee; 61.001(3)(B) excludes independent contractors. The Comptroller's own property-code table (Pub. 96-478, rev. March 2026) puts MS02 'Commissions' at 3 years and MS01 wages at 1 year. The 3-year general rule (72.101) is therefore the test. Verified from the statute and Comptroller text; counsel should confirm only that the agents' contractor status holds (the ICAs and the user say it does).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://statutes.capitol.texas.gov/Docs/PR/htm/PR.72.htm ; https://statutes.capitol.texas.gov/Docs/PR/htm/PR.74.htm ; https://statutes.capitol.texas.gov/Docs/LA/htm/LA.61.htm ; https://www.claimittexas.gov/docs/96-478.pdf ; https://www.claimittexas.gov/app/holder-deadlines ; https://www.claimittexas.gov/app/disclosure-program ; https://www.comptroller.texas.gov/taxes/publications/96-576.php</t>
   </si>
   <si>
     <t xml:space="preserve">Illinois</t>
   </si>
   <si>
-    <t xml:space="preserve">765 ILCS 1026/15-201: 'wages, commissions, bonuses, or reimbursements to which an employee is entitled, or other compensation for personal services' - 1 year after payable. The 'other compensation for personal services' language is broader than Texas and plausibly reaches independent-contractor commissions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">765 ILCS 1026/15-201 catch-all: all other property 3 years after the obligation to pay arises (per secondary sources).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">November 1 for financial, insurance and government holders (confirmed). Deadline for ordinary business holders NOT confirmed from the statute in this session - the prior Illinois act used May 1 with a December 31 cutoff. CONFIRM.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">June 30 for the November 1 filers; business-holder cutoff NOT confirmed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Due-diligence letter by first-class mail for property over $50, sent 60 to 365 days before the report (per Illinois Treasurer guidance summary).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not researched in this session.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Illinois eliminated its business-to-business exemption when it adopted RUUPA (effective 1/1/2018). Chicago's prior-month accrued balance is $0, so Illinois exposure today is only the current-month unbooked deposits.</t>
+    <t xml:space="preserve">765 ILCS 1026/15-201(13): 'wages, commissions, bonuses, or reimbursements to which an employee is entitled, or other compensation for personal services, including amounts held on a payroll card, one year after the amount becomes payable'. The 'other compensation for personal services' clause is not limited to employees, so independent-contractor commissions fall within the 1-year period.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">765 ILCS 1026/15-201(15): property not otherwise specified, 3 years after the earlier of the owner's right to demand it or the obligation to pay or distribute it arising.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before May 1 for business associations other than financial organizations and insurers, covering the immediately preceding calendar year (15-403(b)). Financial organizations, non-life insurers and governments file before November 1 for the 12 months ending June 30 (15-403(a)). Treasurer deadline table: Services / Trade / Manufacturing holders - period ending December 31, due before May 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">December 31 (calendar-year holder; the November 1 / June 30 cycle in the prior draft applies only to financial organizations, insurers and governments)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15-501(a): notice by first-class mail not more than one year nor less than 60 days before filing the report, where the holder has an address not shown to be invalid and the property is $50 or more; also by e-mail where the owner consented to e-mail (15-501(b)).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treasurer VDA program (icash.illinoistreasurer.gov/app/disclosure-program, in place since June 2008): the Treasurer forgoes penalties and interest for holders that are not under examination, complete a self-audit and remit within six months of execution, can support any estimation technique, and accept the agreement without modification. Illinois has no business-to-business exemption under its 2018 Revised Uniform Unclaimed Property Act.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED from the statute text on 10/6/2026: 15-201, 15-403, 15-501 and 15-610 read at ilga.gov (the site presents an incomplete TLS chain and blocks non-browser clients; the pages were fetched with the Sectigo intermediate certificate added and a browser user agent, with certificate verification on); Treasurer reporting guidelines, deadlines and VDA pages read. ANTI-LIMITATION: 15-610(a) - expiration of a period of limitation on the owner's right to receive or recover property, whether specified by CONTRACT, statute or court order, does not prevent the property from being presumed abandoned or affect the holder's duty to report and deliver. 15-610(b): the Treasurer may not enforce more than 10 years after the holder specifically identified the property in a report; the period is tolled where no report was filed.</t>
   </si>
   <si>
     <t xml:space="preserve">SHORT</t>
   </si>
   <si>
-    <t xml:space="preserve">Illinois' 1-year rule reaches 'other compensation for personal services', not only employee wages, so independent-contractor commissions plausibly fall under it. 3-year general rule is the fallback.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.ilga.gov/legislation/ilcs/documents/076510260K15-201.htm ; https://icash.illinoistreasurer.gov/app/faq ; https://www.duanemorris.com/articles/illinois_slides_backward_unclaimed_property_law_0917.html</t>
+    <t xml:space="preserve">15-201(13) reaches 'other compensation for personal services', not only employee wages, so independent-contractor commissions fall under the 1-year period. 3-year catch-all (15-201(15)) is the fallback. Verified from the statute text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.ilga.gov/legislation/ilcs/documents/076510260K15-201.htm ; https://www.ilga.gov/legislation/ilcs/documents/076510260K15-403.htm ; https://www.ilga.gov/legislation/ilcs/documents/076510260K15-501.htm ; https://www.ilga.gov/legislation/ilcs/documents/076510260K15-610.htm ; https://icash.illinoistreasurer.gov/app/reporting-guidelines ; https://icash.illinoistreasurer.gov/app/holder-deadlines ; https://icash.illinoistreasurer.gov/app/disclosure-program</t>
   </si>
   <si>
     <t xml:space="preserve">Pennsylvania</t>
   </si>
   <si>
-    <t xml:space="preserve">Wages / commissions - 2 years per the PA Treasury Dormancy Matrix as summarized in search results (cited there as 72 P.S. 1301.5). NOT verified from the statute text in this session.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">General dormancy period 3 years for most property types (72 P.S. 1301.1 et seq.) per secondary sources.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">April 15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">December 31 (per secondary sources; NOT verified from statute in this session)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Written notice by first-class mail 60 to 120 days before the April 15 deadline for property of $50 or more with a usable address.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA's formal amnesty program ended 10/31/2010. Interest of 12% per year from the date the property was due is cited by secondary sources. Ask PA Treasury about current voluntary compliance terms.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All PA facts come from secondary summaries (PA Treasury Dormancy Matrix as quoted, Sovos, UPPO). Statute and Treasury pages were blocked in this session.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA Treasury's dormancy matrix lists wages/commissions at 2 years without an employee limitation in the sources found. 3-year general rule is the fallback. Not verified from statute text.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.patreasury.gov/pdf/unclaimed-property/Dormancy-Matrix.pdf ; https://www.patreasury.gov/unclaimed-property/holders/ ; https://sovos.com/tax-reporting/unclaimed-property-laws-by-state/pennsylvania/</t>
+    <t xml:space="preserve">72 P.S. 1301.10(2) (Fiscal Code Art. XIII.1, text as published by PA Treasury): 'Wages or other compensation for personal services that have remained unclaimed by the owner for more than two (2) years after the wages or other compensation for personal services become payable or are distributed are presumed abandoned and unclaimed.' Not limited to employees. Treasury's Holder Reporting Handbook and VDA form both describe the exception as 'payroll and commissions - 2 years', and the Dormancy Matrix lists 'Wages/Commissions ... 2'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72 P.S. 1301.10(1): all property not otherwise covered by the Act, held or owing in the ordinary course of the holder's business, unclaimed for more than 3 years after it became payable or distributable. (1301.6, property held by business associations, covers gift cards, stock, dividends, bonds and cooperative distributions and sets no commissions period; the prior draft's citation of 1301.5 for commissions was wrong - 1301.5 is property held by utilities.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">April 15 of the year following the year in which the property became subject to the Commonwealth's custody (1301.11(d)); payment with the report (1301.13(a)); the Treasurer may extend the report date up to six months on written request.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">December 31. Handbook: report year 2026 (due April 15, 2027) covers 2-year property with transactions January 1 - December 31, 2024 and 3-year property with transactions in calendar 2023.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1301.10a: notice to the owner not more than 120 nor less than 60 days before the report is due, by first-class mail (or an electronic method the owner previously agreed to), where the holder has an address not known to be inaccurate and the property is $50 or more; the notice must describe the property, its ownership, its value if known and how to contact the holder; the report must include an affirmation of compliance (1301.10a(d)); no fee may be charged to the owner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treasury Voluntary Disclosure Agreement (searchandclaimpa.gov/docs/PA_Voluntary_Disclosure_Agreement.pdf): Treasury waives penalties and interest under 1301.24 and 1301.25 for property reported within the agreement; the holder must be coming forward voluntarily, not be under audit or self-audit, and not have had voluntary compliance in the past 10 years; 10-year look-back; report within 90 days of execution; no report may be filed before Treasury's signed approval. Without a VDA: interest of 12% per year from when the report was due (1301.24(b)) and a penalty of up to $1,000 per day (1301.24(c)); the Treasurer may waive for good cause and must waive penalties where the holder acted in good faith and without negligence (1301.25(c)). The prior draft's statement that PA's program ended in 2010 referred to a one-time amnesty and is superseded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED on 10/6/2026 from the statute text as published by PA Treasury (PA_UCP_Law.pdf: 1301.6, 1301.10, 1301.10a, 1301.11, 1301.13, 1301.16, 1301.24, 1301.25 read), the Treasury Dormancy Matrix, the Holder Reporting Handbook, the Reporting Guidelines page and the VDA form. The General Assembly's own viewer for 1929 Act 176 Art. XIII.1 (palegis.us) returned only its page shell and its PDF link returned an error, so the Treasury reprint is the text relied on. ANTI-LIMITATION: 1301.16 - expiration of any period specified by STATUTE OR COURT ORDER during which the owner could sue the holder does not prevent custody or affect the duty to report; unlike TX, IL, FL and AL it does NOT mention periods set by contract, and the Act contains no private-escheat prohibition equivalent to Tex. Prop. Code 74.309. The Philly ICA 60-day forfeiture clause is therefore not answered by the Pennsylvania statute either way; it is a contract-law question for counsel. Most Philly items default to Texas, where 74.308 and 74.309 apply.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1301.10(2) reaches 'wages or other compensation for personal services', and Treasury's handbook, matrix and VDA form all describe the 2-year exception as covering commissions. 3-year rule (1301.10(1)) is the fallback. Verified from the statute text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.searchandclaimpa.gov/docs/PA_UCP_Law.pdf ; https://www.patreasury.gov/pdf/unclaimed-property/Dormancy-Matrix.pdf ; https://www.searchandclaimpa.gov/docs/PA_Holder_Reporting_Handbook.pdf ; https://www.searchandclaimpa.gov/app/reporting-guidelines ; https://www.searchandclaimpa.gov/docs/PA_Voluntary_Disclosure_Agreement.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Florida</t>
   </si>
   <si>
-    <t xml:space="preserve">Fla. Stat. 717.115: unpaid WAGES owing in the ordinary course of business unclaimed for more than 1 year after becoming payable. Whether independent-contractor commissions are 'wages' here is not settled in the sources found - if not, the 5-year general rule applies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fla. Stat. 717.102(1): general 5-year dormancy period for other intangible property.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Before May 1, covering the preceding calendar year (Fla. Stat. 717.117)</t>
+    <t xml:space="preserve">Fla. Stat. 717.115: unpaid wages, including wages represented by unpresented payroll checks, owing in the ordinary course of the holder's business and unclaimed for more than 1 year after becoming payable. 'Wages' is not defined in ch. 717 and nothing in the section extends it to independent-contractor commissions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fla. Stat. 717.1035(1): intangible property held by a business association organized or located in Florida is presumed unclaimed 3 years after the date prescribed for payment where the owner's LAST KNOWN ADDRESS IS UNKNOWN. That is exactly the case in which Florida governs a Gallery item under the second priority rule, so 3 years is used here. Where the agent has a Florida address the general rule applies instead: 717.102(1), 5 years after the property becomes payable (change E to 5 for such an item). The prior draft used 5 years.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before May 1, covering the preceding calendar year (717.117(5)); payment with the report (717.119(1)). DFS holder portal: the 2025 report and remittance were due May 1, 2026 for property that reached its dormancy period during the calendar year ending December 31, 2025; 'Florida is NOT a November filing state'.</t>
   </si>
   <si>
     <t xml:space="preserve">December 31</t>
   </si>
   <si>
-    <t xml:space="preserve">Report must list owners with property of $50 or more; due-diligence notice requirement in 717.117 (threshold and timing not verified from statute text in this session).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida has a Voluntary Disclosure program: no penalties, 5-year look-back instead of 10, 2-year audit window after acceptance (per secondary summary of Florida DFS program).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormancy periods and report date confirmed from search summaries of the statute; statute pages blocked. Gallery = Florida is an ASSUMPTION.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fla. Stat. 717.115 covers 'unpaid wages'. Nothing found extends it to independent-contractor commissions, so the 5-year general rule is the likely test. Confirm with counsel.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.flsenate.gov/Laws/Statutes/2024/717.115 ; https://www.flsenate.gov/Laws/Statutes/2024/717.102 ; https://flsenate.gov/Laws/Statutes/2024/717.117 ; https://www.fltreasurehunt.gov/Holder.jsp</t>
+    <t xml:space="preserve">717.117(6): for property of $50 or more, written notice by first-class mail (or e-mail if the owner elected it) not more than 120 nor less than 60 days before filing, where the holder has an address not known to be inaccurate; the notice must carry the statutory heading and give the owner at least 30 days to respond (717.117(7)). Owners of $10 or more are listed by name on the report (717.117(1)(a)).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DFS Voluntary Disclosure Program (fltreasurehunt.gov/Voluntary-Disclosure-Program.jsp; Rule 69G-20.050, F.A.C., effective 12/6/2022): no penalty or interest on the reported property; the holder must not be under examination, must not have filed an annual report before, and must not have been asked to self-audit; the self-audit covers the prior 10 report years and is due within 3 months of the Final Order; estimation methods must be approved by DFS. (The prior draft's 5-year look-back came from a secondary source; the DFS page says ten report years.) Without a VDA: willful failure to report - $500 per day up to $5,000 plus 25% of the value of property not reported (717.134(1)); late report - $10 per day up to $500 (717.117(5)); DFS enforcement is limited to 10 years after the duty arose (717.129(2)).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED from the statute text on 10/6/2026: Fla. Stat. ch. 717 (2024, flsenate.gov) sections 717.102, 717.1035, 717.115, 717.117, 717.119, 717.129 and 717.134 read; DFS VDA page, Rule 69G-20.050 record and holder portal read. The fltreasurehunt.gov/Holder.jsp URL in the prior draft is blocked by the site's firewall; holders are directed to portal.claimyourcashfl.gov. ANTI-LIMITATION: 717.129(1) - expiration of any period specified by CONTRACT, statute or court order during which a claim may be made does not prevent property from being presumed unclaimed or affect the duty to report and deliver. RaySon Partners, LLC is a Florida LLC per the Entity Management Database, which makes 717.1035 (3 years, unknown address) rather than 717.102 (5 years) the operative long period for its unknown-agent items; no Gallery item is older than 5/14/2026, so there is no dollar effect today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">717.115 reaches 'unpaid wages' only; nothing extends it to contractor commissions. For a Florida-organized holder whose owner address is unknown the test is 717.1035 (3 years); where the owner has a Florida address it is 717.102 (5 years). Verified from the statute text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.flsenate.gov/Laws/Statutes/2024/Chapter717/All ; https://www.fltreasurehunt.gov/Voluntary-Disclosure-Program.jsp ; https://www.flrules.org/gateway/ruleno.asp?id=69G-20.050 ; https://portal.claimyourcashfl.gov/UP-Web/sitePages/ReportUnclaimedPropertyHR.jsp</t>
   </si>
   <si>
     <t xml:space="preserve">Alabama</t>
   </si>
   <si>
-    <t xml:space="preserve">Ala. Code 35-12-72: 'wages or other compensation for personal services' presumed abandoned 1 year after the compensation becomes payable. 'Other compensation for personal services' plausibly reaches independent-contractor commissions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ala. Code 35-12-72: all other property 3 years after the owner's right to demand it or the obligation to pay arises, whichever is first.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">November 1, covering the 12 months preceding July 1</t>
+    <t xml:space="preserve">Ala. Code 35-12-72(a)(14): 'Wages or other compensation for personal services, one year after the compensation becomes payable.' Not limited to employees; independent-contractor commissions fall within 'other compensation for personal services'. The Treasurer's dormancy guide lists 'Wages 1' and 'All other property 3' and does not list commissions separately.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ala. Code 35-12-72(a)(18): all other property, 3 years after the owner's right to demand it or the obligation to pay or distribute it arises, whichever first occurs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before November 1, covering the 12 months preceding July 1 (35-12-76(c)); remittance with the report on or before November 1 (35-12-77(e)). Treasurer deadline page: all industry types, period ending June 30, due November 1.</t>
   </si>
   <si>
     <t xml:space="preserve">June 30</t>
   </si>
   <si>
-    <t xml:space="preserve">Aggregate/reporting threshold $50 per secondary sources; due-diligence notice rule (35-12-77) not verified in this session.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormancy periods confirmed from search summaries of the Code; Code pages blocked. Leading Edge = Alabama is an ASSUMPTION.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ala. Code 35-12-72 covers 'wages or other compensation for personal services', so independent-contractor commissions plausibly fall under the 1-year rule. 3-year general rule is the fallback.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://law.justia.com/codes/alabama/2023/title-35/chapter-12/article-2/article-2a/section-35-12-72 ; https://treasury.alabama.gov/alabama-treasury-law/unclaimed-property-law/ ; https://unclaimed.org/reporting/alabama/</t>
+    <t xml:space="preserve">35-12-76(d): written notice to the apparent owner not less than 60 days before filing the report, where the holder has an address not shown to be inaccurate, the owner's claim is not barred by a statute of limitations, and the property is $50 or more. Items under $50 may be reported in aggregate (35-12-76(b)(8); Ala. Admin. Code 892-2-1-.02(5)).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treasurer VDA (unclaimed.alabama.gov/app/disclosure-program): an amnesty agreement under which a holder reports past-due property without interest or penalties for the property covered; Ala. Admin. Code 892-2-1-.02(6) provides that a holder with unreported prior-year property may file a VDA and report without incurring penalties. Without it: $100 per business day up to $5,000 for failing to report or pay, $500 per day up to $25,000 if willful; the Treasurer must waive penalties where the holder acted in good faith (35-12-92).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFIED on 10/6/2026 from the Code text published by the Alabama Treasury (UCP-law.pdf: 35-12-72, 35-12-76, 35-12-77, 35-12-78, 35-12-88, 35-12-92 read), the Treasurer's dormancy guide, reporting guidelines PDF, deadlines and VDA pages, and Ala. Admin. Code ch. 892-2-1. ANTI-LIMITATION: 35-12-88(a) - expiration of a period of limitation on the owner's right to receive or recover property, whether specified by CONTRACT, statute or court order, does not preclude the property from being presumed abandoned or affect the duty to report and deliver. 35-12-88(b): the Treasurer may not enforce more than 10 years after the holder identified the property in a report; tolled where no report was filed. Leading Edge Realty is an Alabama entity per the Entity Management Database.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-12-72(a)(14) reaches 'wages or other compensation for personal services', so independent-contractor commissions fall under the 1-year period. 3-year rule (35-12-72(a)(18)) is the fallback. Verified from the Code text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://treasury.alabama.gov/wp-content/uploads/2024/07/UCP-law.pdf ; https://unclaimed.alabama.gov/docs/Dormancy%20Period%20Guide%20-%202015-final.pdf ; https://unclaimed.alabama.gov/docs/AL_Reporting_Guidelines.pdf ; https://unclaimed.alabama.gov/app/holder-deadlines ; https://unclaimed.alabama.gov/app/disclosure-program ; https://admincode.legislature.state.al.us/api/chapter/892-2-1</t>
   </si>
   <si>
     <t xml:space="preserve">MO</t>
@@ -2282,34 +2285,34 @@
     <t xml:space="preserve">Missouri (HQ / possible state of formation)</t>
   </si>
   <si>
-    <t xml:space="preserve">RSMo 447.536 as amended by HB 1075 (2014): payroll/wages dormancy reduced from 5 to 3 years effective 1/1/2015.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSMo 447.536: general 5-year dormancy period for most property types.</t>
+    <t xml:space="preserve">RSMo 447.536 as amended by HB 1075 (2014): payroll/wages dormancy reduced from 5 to 3 years effective 1/1/2015 (per secondary sources).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSMo 447.536: general 5-year dormancy period for most property types (per secondary sources).</t>
   </si>
   <si>
     <t xml:space="preserve">November 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Due diligence letter required when the owner is due $50 or more (Missouri Treasurer guidance).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missouri matters only under the SECOND priority rule (Texas v. New Jersey, 379 U.S. 674 (1965)): property whose owner address is unknown goes to the holder's state of incorporation/formation - which is the entity's formation state, NOT its headquarters city. Missouri also has a business-to-business exclusion (HB 1075, 2014) for checks/credits owed to a business entity in the ordinary course of business.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missouri's 3-year rule is for payroll checks; commissions to non-employees would fall under the 5-year general rule. Applies only if an LLC is formed in Missouri and the owner's address is unknown.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://revisor.mo.gov/main/OneSection.aspx?section=447.536 ; https://treasurer.mo.gov/UCP/ReportingUnclaimedProperty.aspx ; https://ryan.com/about-ryan/news-and-insights/2014/missouri-legislation-adds-unclaimed-property-business-to-business-exclusions-and-other-changes/</t>
+    <t xml:space="preserve">Due diligence letter required when the owner is due $50 or more (Missouri Treasurer guidance, per secondary sources).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not researched.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT VERIFIED - not researched in the 10/6/2026 verification pass because no holder entity is formed in Missouri (Entity Management Database), so Missouri governs nothing in this population. Missouri matters only under the SECOND priority rule (Texas v. New Jersey, 379 U.S. 674 (1965)): property whose owner address is unknown goes to the holder's state of formation, which is the entity's formation state, NOT its headquarters city. Missouri also has a business-to-business exclusion (HB 1075, 2014) per secondary sources.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missouri's 3-year rule is for payroll checks; commissions to non-employees would fall under the 5-year general rule. Applies only if an LLC is formed in Missouri and the owner's address is unknown. Not verified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://revisor.mo.gov/main/OneSection.aspx?section=447.536 ; https://treasurer.mo.gov/UCP/ReportingUnclaimedProperty.aspx</t>
   </si>
   <si>
     <t xml:space="preserve">District of Columbia</t>
   </si>
   <si>
     <t xml:space="preserve">Not researched - DC accrued balance is $0.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not researched.</t>
   </si>
   <si>
     <t xml:space="preserve">Priority rules (Texas v. New Jersey, 379 U.S. 674 (1965)): (1) the state of the owner's last-known address on the holder's books; (2) if no address, the holder's state of incorporation/formation. The user confirmed that for many older checks the agent is unknown: those items fall under rule (2) and go to the state where each LLC was formed. Per the Entity Management Database that is TEXAS for URE Dallas, URE Houston, Quick Close Properties (TUR), URE Chicago and URE Philadelphia (the last two are Texas LLCs registered as foreign entities in IL and PA), FLORIDA for RaySon Partners d/b/a URE Gallery and ALABAMA for Leading Edge Realty. Not the office's state, and not Kansas City. Private retention of amounts owed to others ('private escheat') is not permitted by any state; an unknown owner does not make the money the company's.</t>
@@ -3868,7 +3871,7 @@
       </c>
       <c r="Q16" s="12" t="n">
         <f aca="false">IFERROR(INDEX('State Rules'!$E$5:$E$11,MATCH($B16,'State Rules'!$A$5:$A$11,0)),"")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R16" s="9" t="n">
         <f aca="false">SUMIFS(Detail!$H:$H,Detail!$A:$A,$A16,Detail!$P:$P,"&lt;="&amp;$B$3)</f>
@@ -20720,7 +20723,7 @@
       </c>
       <c r="Q181" s="22" t="n">
         <f aca="false">IF(E181="","",IFERROR(EDATE(E181,12*INDEX('State Rules'!$E$5:$E$11,MATCH($B181,'State Rules'!$A$5:$A$11,0))),""))</f>
-        <v>47982</v>
+        <v>47252</v>
       </c>
       <c r="R181" s="11" t="str">
         <f aca="false">IF(P181="","",IFERROR(IF(P181&lt;=INDEX('State Rules'!$I$5:$I$11,MATCH($B181,'State Rules'!$A$5:$A$11,0)),"Yes","No"),""))</f>
@@ -20750,7 +20753,7 @@
       </c>
       <c r="AC181" s="22" t="n">
         <f aca="false">IF(AB181="SHORT",P181,IF(AB181="LONG",Q181,""))</f>
-        <v>47982</v>
+        <v>47252</v>
       </c>
       <c r="AD181" s="11" t="str">
         <f aca="false">IF(AB181="SHORT",R181,IF(AB181="LONG",S181,""))</f>
@@ -20808,7 +20811,7 @@
       </c>
       <c r="Q182" s="22" t="n">
         <f aca="false">IF(E182="","",IFERROR(EDATE(E182,12*INDEX('State Rules'!$E$5:$E$11,MATCH($B182,'State Rules'!$A$5:$A$11,0))),""))</f>
-        <v>48028</v>
+        <v>47298</v>
       </c>
       <c r="R182" s="11" t="str">
         <f aca="false">IF(P182="","",IFERROR(IF(P182&lt;=INDEX('State Rules'!$I$5:$I$11,MATCH($B182,'State Rules'!$A$5:$A$11,0)),"Yes","No"),""))</f>
@@ -20838,7 +20841,7 @@
       </c>
       <c r="AC182" s="22" t="n">
         <f aca="false">IF(AB182="SHORT",P182,IF(AB182="LONG",Q182,""))</f>
-        <v>48028</v>
+        <v>47298</v>
       </c>
       <c r="AD182" s="11" t="str">
         <f aca="false">IF(AB182="SHORT",R182,IF(AB182="LONG",S182,""))</f>
@@ -20898,7 +20901,7 @@
       </c>
       <c r="Q183" s="22" t="n">
         <f aca="false">IF(E183="","",IFERROR(EDATE(E183,12*INDEX('State Rules'!$E$5:$E$11,MATCH($B183,'State Rules'!$A$5:$A$11,0))),""))</f>
-        <v>48074</v>
+        <v>47344</v>
       </c>
       <c r="R183" s="11" t="str">
         <f aca="false">IF(P183="","",IFERROR(IF(P183&lt;=INDEX('State Rules'!$I$5:$I$11,MATCH($B183,'State Rules'!$A$5:$A$11,0)),"Yes","No"),""))</f>
@@ -20928,7 +20931,7 @@
       </c>
       <c r="AC183" s="22" t="n">
         <f aca="false">IF(AB183="SHORT",P183,IF(AB183="LONG",Q183,""))</f>
-        <v>48074</v>
+        <v>47344</v>
       </c>
       <c r="AD183" s="11" t="str">
         <f aca="false">IF(AB183="SHORT",R183,IF(AB183="LONG",S183,""))</f>
@@ -20988,7 +20991,7 @@
       </c>
       <c r="Q184" s="22" t="n">
         <f aca="false">IF(E184="","",IFERROR(EDATE(E184,12*INDEX('State Rules'!$E$5:$E$11,MATCH($B184,'State Rules'!$A$5:$A$11,0))),""))</f>
-        <v>48074</v>
+        <v>47344</v>
       </c>
       <c r="R184" s="11" t="str">
         <f aca="false">IF(P184="","",IFERROR(IF(P184&lt;=INDEX('State Rules'!$I$5:$I$11,MATCH($B184,'State Rules'!$A$5:$A$11,0)),"Yes","No"),""))</f>
@@ -21018,7 +21021,7 @@
       </c>
       <c r="AC184" s="22" t="n">
         <f aca="false">IF(AB184="SHORT",P184,IF(AB184="LONG",Q184,""))</f>
-        <v>48074</v>
+        <v>47344</v>
       </c>
       <c r="AD184" s="11" t="str">
         <f aca="false">IF(AB184="SHORT",R184,IF(AB184="LONG",S184,""))</f>
@@ -23696,7 +23699,7 @@
         <v>685</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>46568</v>
+        <v>46387</v>
       </c>
       <c r="J6" s="15" t="s">
         <v>686</v>
@@ -23778,7 +23781,7 @@
         <v>703</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>704</v>
@@ -23843,42 +23846,42 @@
         <v>717</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>687</v>
+        <v>718</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M9" s="28" t="s">
         <v>689</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O9" s="15" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C10" s="28" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E10" s="28" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>716</v>
@@ -23887,22 +23890,22 @@
         <v>46568</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>687</v>
+        <v>728</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="M10" s="28" t="s">
         <v>678</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="O10" s="15" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23910,15 +23913,15 @@
         <v>56</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="15" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E11" s="28"/>
       <c r="F11" s="15" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
@@ -23926,17 +23929,17 @@
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
       <c r="L11" s="15" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="M11" s="28"/>
       <c r="N11" s="15" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="O11" s="15"/>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -23955,7 +23958,7 @@
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>

--- a/accrued-commissions-analysis/Accrued_Commissions_Unclaimed_Property_Analysis.xlsx
+++ b/accrued-commissions-analysis/Accrued_Commissions_Unclaimed_Property_Analysis.xlsx
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="744">
   <si>
     <t xml:space="preserve">Accrued Commissions - Unclaimed Property Exposure by Entity</t>
   </si>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">Dormant at next report cutoff - LONG - likely-commission + memo-flagged</t>
   </si>
   <si>
-    <t xml:space="preserve">Likely test given independent-contractor agents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormant today - LIKELY test - likely-commission + memo-flagged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormant at next report cutoff - LIKELY test - likely-commission + memo-flagged</t>
+    <t xml:space="preserve">Adopted test given independent-contractor agents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormant today - ADOPTED test - likely-commission + memo-flagged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormant at next report cutoff - ADOPTED test - likely-commission + memo-flagged</t>
   </si>
   <si>
     <t xml:space="preserve">Oldest item</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">How to read this</t>
   </si>
   <si>
-    <t xml:space="preserve">Classification (Detail col N) uses the fee amounts in rows 4-7 and the threshold in B8: an exact fee amount = presumed company revenue (keep; book to revenue, not unclaimed property). At or under the threshold = likely fee, review. Memo-flagged = memo says not ours / unknown agent / duplicate / legal hold (owed back to the payer or needs resolution). Everything else = larger amount that likely includes an agent's commission split - this is the unclaimed-property population.</t>
+    <t xml:space="preserve">Classification (Detail col N) uses the fee amounts in rows 4-7 and the threshold in B8: an exact fee amount = company revenue, not unclaimed property. Decision 10/6/2026: fee checks are NOT moved to revenue en masse; they are recognized through the ordinary matching process and the year-end revenue true-up, and only an item being written off at a quarterly threshold review is booked to revenue at that time. At or under the threshold = likely fee, review. Memo-flagged = memo says not ours / unknown agent / duplicate / legal hold (owed back to the payer or needs resolution). Everything else = larger amount that likely includes an agent's commission split - this is the unclaimed-property population.</t>
   </si>
   <si>
     <t xml:space="preserve">Columns R-S apply the dormancy tests to ALL unbooked items (upper bound). Columns T-W apply them only to the likely-commission and memo-flagged items. Even the T-W figures are upper bounds: within a larger check, only the agent's share (typically the check less the company's fee / split) is reportable; the company's share is revenue.</t>
   </si>
   <si>
-    <t xml:space="preserve">SHORT test = the state's period for wages / compensation for personal services. LONG test = the general catch-all period. Column X picks the likely test for each entity's default governing state now that agents are confirmed to be independent contractors (Texas and Florida: LONG; Illinois, Pennsylvania, Alabama: SHORT), and columns Y-Z apply it item by item, so an item whose owner state has been filled in uses its own state's test. See State Rules cols M-N for the reasoning; it is a legal judgment for counsel to confirm.</t>
+    <t xml:space="preserve">SHORT test = the state's period for wages / compensation for personal services. LONG test = the general catch-all period. Column X picks the likely test for each entity's default governing state now that agents are confirmed to be independent contractors (Texas and Florida: LONG; Illinois, Pennsylvania, Alabama: SHORT), and columns Y-Z apply it item by item, so an item whose owner state has been filled in uses its own state's test. See State Rules cols M-N for the basis. Management adopted these tests on 10/6/2026 after the statutes were verified; Texas applies the 3-year rule and the 1-year wage rule is not used.</t>
   </si>
   <si>
     <t xml:space="preserve">Unknown agent = second priority rule. Per the Entity Management Database, URE Dallas, URE Houston, Quick Close Properties (TUR), URE Chicago and URE Philadelphia are all TEXAS LLCs; Gallery (RaySon Partners) is Florida; Leading Edge Realty is Alabama. Column B holds that formation state as each entity's DEFAULT governing state, so unknown-agent items at Chicago and Philly are tested under TEXAS rules (3-year general period for contractor commissions), not Illinois or Pennsylvania. When an agent's last-known address state is entered in Detail col U, that item switches to the address state's rules (first priority rule). Office state is shown in col AB for reference.</t>
@@ -398,13 +398,13 @@
     <t xml:space="preserve">Heuristic reportable population $ (larger-amount + memo-flagged items)</t>
   </si>
   <si>
-    <t xml:space="preserve">Likely test for this item's governing state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormant date - LIKELY test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormant at next cutoff - LIKELY test?</t>
+    <t xml:space="preserve">Adopted test for this item's governing state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormant date - ADOPTED test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormant at next cutoff - ADOPTED test?</t>
   </si>
   <si>
     <t xml:space="preserve">1839</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">ICA CLAUSES THAT REDUCE WHAT IS OWED TO AGENTS - legal question</t>
   </si>
   <si>
-    <t xml:space="preserve">Every ICA lets the Broker hold or apply commissions against amounts the agent owes (dues, fees, E&amp;O deductibles, indemnity) and conditions post-termination payouts on dues being paid in full. The Philly ICA goes further: an incomplete file 30 days past closing is paid 50/50 and 60 days past closing is 'forfeited'; a license not reactivated within 30 days means 'brokerage will keep 100% of commission'. TUR's agreement forfeits accrued commissions if the agent collects in their own name or breaches Section 5. A documented offset reduces the agent's share dollar for dollar. A contractual forfeiture is less certain. Verified 10/6/2026: Texas (Prop. Code 74.308), Illinois (765 ILCS 1026/15-610(a)), Florida (717.129(1)) and Alabama (35-12-88(a)) each say that the expiration of a period specified by CONTRACT does not prevent property from being presumed abandoned, and Texas 74.309 separately bars taking funds into income by private agreement to circumvent the unclaimed property process. Pennsylvania's 1301.16 mentions only statute and court order, not contract, and has no private-escheat section, so the Philly clause is a contract-law question there; but most Philly items default to Texas, where 74.308-74.309 apply. Whether any state would honor these clauses against an escheat claim is for counsel. Do not treat a forfeiture as the company's money until counsel says so AND the triggering facts (closing date, file status at day 60, termination date) are documented per item. See the ICA Terms tab.</t>
+    <t xml:space="preserve">Every ICA lets the Broker hold or apply commissions against amounts the agent owes (dues, fees, E&amp;O deductibles, indemnity) and conditions post-termination payouts on dues being paid in full. The Philly ICA goes further: an incomplete file 30 days past closing is paid 50/50 and 60 days past closing is 'forfeited'; a license not reactivated within 30 days means 'brokerage will keep 100% of commission'. TUR's agreement forfeits accrued commissions if the agent collects in their own name or breaches Section 5. A documented offset reduces the agent's share dollar for dollar. A contractual forfeiture is less certain. Verified 10/6/2026: Texas (Prop. Code 74.308), Illinois (765 ILCS 1026/15-610(a)), Florida (717.129(1)) and Alabama (35-12-88(a)) each say that the expiration of a period specified by CONTRACT does not prevent property from being presumed abandoned, and Texas 74.309 separately bars taking funds into income by private agreement to circumvent the unclaimed property process. Pennsylvania's 1301.16 mentions only statute and court order, not contract, and has no private-escheat section, so the Philly clause is a contract-law question there; but most Philly items default to Texas, where 74.308-74.309 apply. DECISION 10/6/2026: the company does not rely on the forfeiture clauses against an escheat claim. An item past dormancy is paid or reported at the agent's share regardless of the Philly 60-day / license clauses or the TUR breach clauses. Documented offsets still reduce the agent's share dollar for dollar. See the ICA Terms tab.</t>
   </si>
   <si>
     <t xml:space="preserve">Counsel; Accounting to document per item.</t>
@@ -1760,10 +1760,34 @@
     <t xml:space="preserve">Counsel.</t>
   </si>
   <si>
+    <t xml:space="preserve">DECISION: revenue timing for fee checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fee checks and confirmed small items are company revenue and are not unclaimed property, but they are NOT moved to revenue en masse. They stay in the accrued balance and are recognized when matched in the ordinary course and through the year-end revenue true-up, which already captures them. At a quarterly threshold review only an item that is being written off at that time is booked to revenue (decision 10/6/2026).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Financial Reporting and Analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DECISION: process owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The quarterly threshold review and the annual state filings are owned by the Director of Financial Reporting and Analysis, with counsel; the CFO approves any VDA and any retention under an offset (decision 10/6/2026).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFTER REMITTANCE: the agent later submits the file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good-faith delivery to the state relieves the holder of liability for the property in every state in scope (Tex. Prop. Code 74.304(b)-(c); 72 P.S. 1301.14; Fla. Stat. 717.1201(1); Ala. Code 35-12-79(b); 765 ILCS 1026/15-604). The transaction is still processed and the agent is still paid: either the agent claims the money from the state, or the company pays the agent and files for reimbursement from the state (Texas 74.502: the Comptroller reimburses a valid claim paid by the holder; Pennsylvania 1301.14: reimbursement with interest; Florida 717.1201(3); Alabama 35-12-79(c); Illinois 15-605). The company's fee on that transaction is revenue as usual. Keep the state report reference on the Paperless Pipeline transaction so the reimbursement claim can be filed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Financial Reporting and Analysis / Accounting.</t>
+  </si>
+  <si>
     <t xml:space="preserve">VERIFIED 10/6/2026 - and what is still open</t>
   </si>
   <si>
-    <t xml:space="preserve">Every rule on the State Rules tab for TX, IL, PA, FL and AL (periods, section numbers, report cutoff and due date, due-diligence threshold and timing, VDA terms, anti-limitation provision) was read from the statute text and the state treasury pages on 10/6/2026; the URLs are in the Sources column. Corrections made: IL business holders file by May 1 for the calendar year (not November 1 / June 30); FL's operative long period for a Florida holder with an unknown owner address is 3 years under 717.1035 (not 5); the PA commissions rule is 1301.10(2) (not 1301.5); PA, FL and TX VDA descriptions replaced with the treasury pages' own terms. STILL OPEN: (1) no court decision or Comptroller ruling specifically on broker-to-agent commissions was found - the Texas 3-year position rests on the statutory definitions and the Comptroller's MS02 table; (2) whether a court would enforce the Philly ICA 60-day forfeiture against an escheat claim (the PA statute is silent on contract-based bars; TX 74.308-74.309 cut against it); (3) deposit date is a proxy for the payable date; (4) Missouri and DC not researched (no holder formed there, DC balance $0); (5) Texas VDA eligibility for an entity that has filed before is not stated on the Comptroller pages - ask when requesting.</t>
+    <t xml:space="preserve">Every rule on the State Rules tab for TX, IL, PA, FL and AL (periods, section numbers, report cutoff and due date, due-diligence threshold and timing, VDA terms, anti-limitation provision) was read from the statute text and the state treasury pages on 10/6/2026; the URLs are in the Sources column. Corrections made: IL business holders file by May 1 for the calendar year (not November 1 / June 30); FL's operative long period for a Florida holder with an unknown owner address is 3 years under 717.1035 (not 5); the PA commissions rule is 1301.10(2) (not 1301.5); PA, FL and TX VDA descriptions replaced with the treasury pages' own terms. POSITIONS ADOPTED 10/6/2026: Texas applies the 3-year rule (no court decision or Comptroller ruling specifically on broker-to-agent commissions was found; the position rests on the statutory definitions and the Comptroller's MS02 table); the Philly and TUR forfeiture clauses are not relied on against an escheat claim. STILL OPEN for counsel's confirmation: (1) deposit date is a proxy for the payable date; (2) Missouri and DC not researched (no holder formed there, DC balance $0); (3) Texas VDA eligibility for an entity that has filed before is not stated on the Comptroller pages - ask when requesting.</t>
   </si>
   <si>
     <t xml:space="preserve">Counsel / unclaimed-property advisor.</t>
@@ -2114,7 +2138,7 @@
     <t xml:space="preserve">Verification status</t>
   </si>
   <si>
-    <t xml:space="preserve">Likely test for independent-contractor commissions (SHORT/LONG)</t>
+    <t xml:space="preserve">Adopted test for independent-contractor commissions (SHORT/LONG)</t>
   </si>
   <si>
     <t xml:space="preserve">Why</t>
@@ -2150,7 +2174,7 @@
     <t xml:space="preserve">LONG</t>
   </si>
   <si>
-    <t xml:space="preserve">Agents are independent contractors (confirmed by user). 72.1015 reaches only 'wages' as defined in Labor Code 61.001(7): compensation owed by an employer to an employee; 61.001(3)(B) excludes independent contractors. The Comptroller's own property-code table (Pub. 96-478, rev. March 2026) puts MS02 'Commissions' at 3 years and MS01 wages at 1 year. The 3-year general rule (72.101) is therefore the test. Verified from the statute and Comptroller text; counsel should confirm only that the agents' contractor status holds (the ICAs and the user say it does).</t>
+    <t xml:space="preserve">Agents are independent contractors (confirmed by user). 72.1015 reaches only 'wages' as defined in Labor Code 61.001(7): compensation owed by an employer to an employee; 61.001(3)(B) excludes independent contractors. The Comptroller's own property-code table (Pub. 96-478, rev. March 2026) puts MS02 'Commissions' at 3 years and MS01 wages at 1 year. The 3-year general rule (72.101) is the test. ADOPTED by management on 10/6/2026 after the statute and Comptroller text were verified; the 1-year wage rule is not applied.</t>
   </si>
   <si>
     <t xml:space="preserve">https://statutes.capitol.texas.gov/Docs/PR/htm/PR.72.htm ; https://statutes.capitol.texas.gov/Docs/PR/htm/PR.74.htm ; https://statutes.capitol.texas.gov/Docs/LA/htm/LA.61.htm ; https://www.claimittexas.gov/docs/96-478.pdf ; https://www.claimittexas.gov/app/holder-deadlines ; https://www.claimittexas.gov/app/disclosure-program ; https://www.comptroller.texas.gov/taxes/publications/96-576.php</t>
@@ -2318,7 +2342,7 @@
     <t xml:space="preserve">Priority rules (Texas v. New Jersey, 379 U.S. 674 (1965)): (1) the state of the owner's last-known address on the holder's books; (2) if no address, the holder's state of incorporation/formation. The user confirmed that for many older checks the agent is unknown: those items fall under rule (2) and go to the state where each LLC was formed. Per the Entity Management Database that is TEXAS for URE Dallas, URE Houston, Quick Close Properties (TUR), URE Chicago and URE Philadelphia (the last two are Texas LLCs registered as foreign entities in IL and PA), FLORIDA for RaySon Partners d/b/a URE Gallery and ALABAMA for Leading Edge Realty. Not the office's state, and not Kansas City. Private retention of amounts owed to others ('private escheat') is not permitted by any state; an unknown owner does not make the money the company's.</t>
   </si>
   <si>
-    <t xml:space="preserve">Blue = hardcoded inputs you can change. All dormancy periods are expressed in years and are applied from the DEPOSIT DATE in the cash-requirements workbook as a proxy for the date the amount became payable - the true trigger is when the agent's share became payable, which may be earlier (closing date) or later.</t>
+    <t xml:space="preserve">Blue = hardcoded inputs you can change. Tests in col M were adopted by management on 10/6/2026 after verification (Texas: 3-year rule). All dormancy periods are expressed in years and are applied from the DEPOSIT DATE in the cash-requirements workbook as a proxy for the date the amount became payable - the true trigger is when the agent's share became payable, which may be earlier (closing date) or later.</t>
   </si>
 </sst>
 </file>
@@ -22541,7 +22565,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -22833,6 +22857,48 @@
       </c>
       <c r="D22" s="15" t="s">
         <v>551</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>552</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>553</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>554</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>557</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>558</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -22864,12 +22930,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -22882,19 +22948,19 @@
         <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22902,19 +22968,19 @@
         <v>37</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22923,16 +22989,16 @@
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22941,16 +23007,16 @@
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22959,16 +23025,16 @@
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22977,16 +23043,16 @@
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22994,19 +23060,19 @@
         <v>44</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23015,16 +23081,16 @@
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23032,19 +23098,19 @@
         <v>40</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23053,16 +23119,16 @@
       </c>
       <c r="B13" s="15"/>
       <c r="C13" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23071,16 +23137,16 @@
       </c>
       <c r="B14" s="15"/>
       <c r="C14" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23089,16 +23155,16 @@
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23106,19 +23172,19 @@
         <v>42</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23127,16 +23193,16 @@
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23145,16 +23211,16 @@
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23163,16 +23229,16 @@
       </c>
       <c r="B19" s="15"/>
       <c r="C19" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23181,16 +23247,16 @@
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23198,19 +23264,19 @@
         <v>47</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23219,16 +23285,16 @@
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23237,16 +23303,16 @@
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23255,16 +23321,16 @@
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23273,56 +23339,56 @@
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -23352,12 +23418,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -23371,7 +23437,7 @@
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -23385,7 +23451,7 @@
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -23399,7 +23465,7 @@
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -23413,7 +23479,7 @@
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -23427,7 +23493,7 @@
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -23441,7 +23507,7 @@
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -23455,7 +23521,7 @@
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -23469,7 +23535,7 @@
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -23483,7 +23549,7 @@
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -23497,7 +23563,7 @@
     </row>
     <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -23558,12 +23624,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -23581,49 +23647,49 @@
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23631,46 +23697,46 @@
         <v>38</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="C5" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="I5" s="29" t="n">
         <v>46447</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="M5" s="28" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23678,46 +23744,46 @@
         <v>45</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="C6" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="E6" s="28" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="I6" s="29" t="n">
         <v>46387</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="M6" s="28" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23725,46 +23791,46 @@
         <v>48</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="C7" s="28" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>3</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="I7" s="29" t="n">
         <v>46387</v>
       </c>
       <c r="J7" s="15" t="s">
+        <v>705</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>706</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>707</v>
+      </c>
+      <c r="M7" s="28" t="s">
         <v>697</v>
       </c>
-      <c r="K7" s="15" t="s">
-        <v>698</v>
-      </c>
-      <c r="L7" s="15" t="s">
-        <v>699</v>
-      </c>
-      <c r="M7" s="28" t="s">
-        <v>689</v>
-      </c>
       <c r="N7" s="15" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23772,46 +23838,46 @@
         <v>51</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="C8" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="E8" s="28" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="I8" s="29" t="n">
         <v>46387</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="M8" s="28" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="O8" s="15" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23819,93 +23885,93 @@
         <v>54</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="C9" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="I9" s="29" t="n">
         <v>46568</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="M9" s="28" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="O9" s="15" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="C10" s="28" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="E10" s="28" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="I10" s="29" t="n">
         <v>46568</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="M10" s="28" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="O10" s="15" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23913,15 +23979,15 @@
         <v>56</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="15" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="E11" s="28"/>
       <c r="F11" s="15" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
@@ -23929,17 +23995,17 @@
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
       <c r="L11" s="15" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="M11" s="28"/>
       <c r="N11" s="15" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="O11" s="15"/>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -23958,7 +24024,7 @@
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>

--- a/accrued-commissions-analysis/Accrued_Commissions_Unclaimed_Property_Analysis.xlsx
+++ b/accrued-commissions-analysis/Accrued_Commissions_Unclaimed_Property_Analysis.xlsx
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="749">
   <si>
     <t xml:space="preserve">Accrued Commissions - Unclaimed Property Exposure by Entity</t>
   </si>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">How to read this</t>
   </si>
   <si>
-    <t xml:space="preserve">Classification (Detail col N) uses the fee amounts in rows 4-7 and the threshold in B8: an exact fee amount = company revenue, not unclaimed property. Decision 10/6/2026: fee checks are NOT moved to revenue en masse; they are recognized through the ordinary matching process and the year-end revenue true-up, and only an item being written off at a quarterly threshold review is booked to revenue at that time. At or under the threshold = likely fee, review. Memo-flagged = memo says not ours / unknown agent / duplicate / legal hold (owed back to the payer or needs resolution). Everything else = larger amount that likely includes an agent's commission split - this is the unclaimed-property population.</t>
+    <t xml:space="preserve">Classification (Detail col N) uses the fee amounts in rows 4-7 and the threshold in B8: an exact fee amount = company revenue, not unclaimed property. Decision 10/6/2026: fee checks are NOT moved to revenue en masse; they are recognized through the ordinary matching process and the year-end revenue true-up, and only an item being written off at a semi-annual threshold review is booked to revenue at that time. At or under the threshold = likely fee, review. Memo-flagged = memo says not ours / unknown agent / duplicate / legal hold (owed back to the payer or needs resolution). Everything else = larger amount that likely includes an agent's commission split - this is the unclaimed-property population.</t>
   </si>
   <si>
     <t xml:space="preserve">Columns R-S apply the dormancy tests to ALL unbooked items (upper bound). Columns T-W apply them only to the likely-commission and memo-flagged items. Even the T-W figures are upper bounds: within a larger check, only the agent's share (typically the check less the company's fee / split) is reportable; the company's share is revenue.</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">DECISION: revenue timing for fee checks</t>
   </si>
   <si>
-    <t xml:space="preserve">Fee checks and confirmed small items are company revenue and are not unclaimed property, but they are NOT moved to revenue en masse. They stay in the accrued balance and are recognized when matched in the ordinary course and through the year-end revenue true-up, which already captures them. At a quarterly threshold review only an item that is being written off at that time is booked to revenue (decision 10/6/2026).</t>
+    <t xml:space="preserve">Fee checks and confirmed small items are company revenue and are not unclaimed property, but they are NOT moved to revenue en masse. They stay in the accrued balance and are recognized when matched in the ordinary course and through the year-end revenue true-up, which already captures them. At a semi-annual threshold review only an item that is being written off at that time is booked to revenue (decision 10/6/2026).</t>
   </si>
   <si>
     <t xml:space="preserve">Director of Financial Reporting and Analysis.</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">DECISION: process owner</t>
   </si>
   <si>
-    <t xml:space="preserve">The quarterly threshold review and the annual state filings are owned by the Director of Financial Reporting and Analysis, with counsel; the CFO approves any VDA and any retention under an offset (decision 10/6/2026).</t>
+    <t xml:space="preserve">The semi-annual threshold review and the annual state filings are owned by the Director of Financial Reporting and Analysis, with counsel; the CFO approves any VDA and any retention under an offset (decision 10/6/2026).</t>
   </si>
   <si>
     <t xml:space="preserve">AFTER REMITTANCE: the agent later submits the file</t>
@@ -1782,6 +1782,21 @@
   </si>
   <si>
     <t xml:space="preserve">Director of Financial Reporting and Analysis / Accounting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DECISION: review cadence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The threshold review runs twice a year, in early December (as of November 30, projected to the December 31 cutoffs for PA, IL and FL and the March 1 Texas cutoff) and early June (as of May 31, projected to the June 30 Alabama cutoff and the July 1 Texas remittance). The December review must finish before Pennsylvania's letter window closes on February 14; Texas letters go out by May 2 (decision 10/6/2026).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IF A CUTOFF IS MISSED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The item becomes past-due property and goes on the next report with its original dormancy date; nothing is forfeited. Verified consequences: Texas 10% interest a year from the original due date (74.705) plus a 5% penalty and a further 5% if more than 30 days late (74.706), waivable for a good-faith effort (74.707); Pennsylvania 12% interest (1301.24(b)) plus up to $1,000 a day (1301.24(c)), penalties waived for a good-faith, non-negligent holder (1301.25(c)); Florida $10 a day up to $500 for a late report (717.117(5)) and, if wilful, $500 a day up to $5,000 plus 25% of the unreported value (717.134), waived for good faith; Alabama $100 per business day up to $5,000, $500 a day up to $25,000 if wilful, waived for good faith (35-12-92); Illinois penalties and interest under the Act (not read in detail), forgone under the VDA. Enforcement windows run from a FILED report (TX 7 years, PA 15, IL and AL 10, FL 10 from the duty) and are tolled where nothing was reported, so unreported is worse than late.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Financial Reporting and Analysis / counsel.</t>
   </si>
   <si>
     <t xml:space="preserve">VERIFIED 10/6/2026 - and what is still open</t>
@@ -22565,7 +22580,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -22898,7 +22913,35 @@
         <v>558</v>
       </c>
       <c r="D25" s="15" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="27" t="s">
         <v>559</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>560</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>562</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>563</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>564</v>
       </c>
     </row>
   </sheetData>
@@ -22930,12 +22973,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -22948,19 +22991,19 @@
         <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22968,19 +23011,19 @@
         <v>37</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22989,16 +23032,16 @@
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23007,16 +23050,16 @@
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23025,16 +23068,16 @@
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23043,16 +23086,16 @@
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23060,19 +23103,19 @@
         <v>44</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23081,16 +23124,16 @@
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23098,19 +23141,19 @@
         <v>40</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23119,16 +23162,16 @@
       </c>
       <c r="B13" s="15"/>
       <c r="C13" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23137,16 +23180,16 @@
       </c>
       <c r="B14" s="15"/>
       <c r="C14" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23155,16 +23198,16 @@
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23172,19 +23215,19 @@
         <v>42</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23193,16 +23236,16 @@
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23211,16 +23254,16 @@
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23229,16 +23272,16 @@
       </c>
       <c r="B19" s="15"/>
       <c r="C19" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23247,16 +23290,16 @@
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23264,19 +23307,19 @@
         <v>47</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23285,16 +23328,16 @@
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23303,16 +23346,16 @@
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23321,16 +23364,16 @@
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23339,56 +23382,56 @@
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
   </sheetData>
@@ -23418,12 +23461,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -23437,7 +23480,7 @@
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -23451,7 +23494,7 @@
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -23465,7 +23508,7 @@
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -23479,7 +23522,7 @@
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -23493,7 +23536,7 @@
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -23507,7 +23550,7 @@
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -23521,7 +23564,7 @@
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -23535,7 +23578,7 @@
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -23549,7 +23592,7 @@
     </row>
     <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -23563,7 +23606,7 @@
     </row>
     <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -23624,12 +23667,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -23647,49 +23690,49 @@
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23697,46 +23740,46 @@
         <v>38</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="C5" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="I5" s="29" t="n">
         <v>46447</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="M5" s="28" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23744,46 +23787,46 @@
         <v>45</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="C6" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="E6" s="28" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="I6" s="29" t="n">
         <v>46387</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="M6" s="28" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23791,46 +23834,46 @@
         <v>48</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="C7" s="28" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>3</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="I7" s="29" t="n">
         <v>46387</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="M7" s="28" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23838,46 +23881,46 @@
         <v>51</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="C8" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="E8" s="28" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="I8" s="29" t="n">
         <v>46387</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="M8" s="28" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="O8" s="15" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23885,93 +23928,93 @@
         <v>54</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="C9" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="I9" s="29" t="n">
         <v>46568</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="M9" s="28" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="O9" s="15" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="C10" s="28" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="E10" s="28" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="I10" s="29" t="n">
         <v>46568</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="M10" s="28" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="O10" s="15" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23979,15 +24022,15 @@
         <v>56</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="15" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="E11" s="28"/>
       <c r="F11" s="15" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
@@ -23995,17 +24038,17 @@
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
       <c r="L11" s="15" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="M11" s="28"/>
       <c r="N11" s="15" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="O11" s="15"/>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -24024,7 +24067,7 @@
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>

--- a/accrued-commissions-analysis/Accrued_Commissions_Unclaimed_Property_Analysis.xlsx
+++ b/accrued-commissions-analysis/Accrued_Commissions_Unclaimed_Property_Analysis.xlsx
@@ -293,7 +293,7 @@
     <t xml:space="preserve">How to read this</t>
   </si>
   <si>
-    <t xml:space="preserve">Classification (Detail col N) uses the fee amounts in rows 4-7 and the threshold in B8: an exact fee amount = company revenue, not unclaimed property. Decision 10/6/2026: fee checks are NOT moved to revenue en masse; they are recognized through the ordinary matching process and the year-end revenue true-up, and only an item being written off at a semi-annual threshold review is booked to revenue at that time. At or under the threshold = likely fee, review. Memo-flagged = memo says not ours / unknown agent / duplicate / legal hold (owed back to the payer or needs resolution). Everything else = larger amount that likely includes an agent's commission split - this is the unclaimed-property population.</t>
+    <t xml:space="preserve">Classification (Detail col N) uses the fee amounts in rows 4-7 and the threshold in B8: an exact fee amount = company revenue, not unclaimed property. Decision 10/6/2026: fee checks are NOT moved to revenue en masse; they are recognized through the ordinary matching process and the year-end revenue true-up, and only an item being written off at the annual threshold review is booked to revenue at that time. At or under the threshold = likely fee, review. Memo-flagged = memo says not ours / unknown agent / duplicate / legal hold (owed back to the payer or needs resolution). Everything else = larger amount that likely includes an agent's commission split - this is the unclaimed-property population.</t>
   </si>
   <si>
     <t xml:space="preserve">Columns R-S apply the dormancy tests to ALL unbooked items (upper bound). Columns T-W apply them only to the likely-commission and memo-flagged items. Even the T-W figures are upper bounds: within a larger check, only the agent's share (typically the check less the company's fee / split) is reportable; the company's share is revenue.</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">DECISION: revenue timing for fee checks</t>
   </si>
   <si>
-    <t xml:space="preserve">Fee checks and confirmed small items are company revenue and are not unclaimed property, but they are NOT moved to revenue en masse. They stay in the accrued balance and are recognized when matched in the ordinary course and through the year-end revenue true-up, which already captures them. At a semi-annual threshold review only an item that is being written off at that time is booked to revenue (decision 10/6/2026).</t>
+    <t xml:space="preserve">Fee checks and confirmed small items are company revenue and are not unclaimed property, but they are NOT moved to revenue en masse. They stay in the accrued balance and are recognized when matched in the ordinary course and through the year-end revenue true-up, which already captures them. At the annual threshold review only an item that is being written off at that time is booked to revenue (decision 10/6/2026).</t>
   </si>
   <si>
     <t xml:space="preserve">Director of Financial Reporting and Analysis.</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">DECISION: process owner</t>
   </si>
   <si>
-    <t xml:space="preserve">The semi-annual threshold review and the annual state filings are owned by the Director of Financial Reporting and Analysis, with counsel; the CFO approves any VDA and any retention under an offset (decision 10/6/2026).</t>
+    <t xml:space="preserve">The annual threshold review and the state filings are owned by the Director of Financial Reporting and Analysis, with counsel; the CFO approves any VDA and any retention under an offset (decision 10/6/2026).</t>
   </si>
   <si>
     <t xml:space="preserve">AFTER REMITTANCE: the agent later submits the file</t>
@@ -1784,10 +1784,10 @@
     <t xml:space="preserve">Director of Financial Reporting and Analysis / Accounting.</t>
   </si>
   <si>
-    <t xml:space="preserve">DECISION: review cadence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The threshold review runs twice a year, in early December (as of November 30, projected to the December 31 cutoffs for PA, IL and FL and the March 1 Texas cutoff) and early June (as of May 31, projected to the June 30 Alabama cutoff and the July 1 Texas remittance). The December review must finish before Pennsylvania's letter window closes on February 14; Texas letters go out by May 2 (decision 10/6/2026).</t>
+    <t xml:space="preserve">DECISION: review cadence - one annual cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The threshold review runs once a year, in early December (as of November 30), projected forward to every state cutoff: December 31 for PA, IL and FL; March 1 for Texas; June 30 for Alabama. One batch of due-diligence letters goes out between January 1 and February 14, which is inside the PA (Dec 16 - Feb 14) and FL (Jan 1 - Mar 2) windows and earlier than IL, TX and AL require. Reports are prepared in the same cycle and submitted on each state's statutory date: PA April 15, IL and FL May 1, TX July 1, AL November 1. The review must finish before February 14. Not verified: whether TX and IL accept a report filed months early and whether AL accepts early remittance (decision 10/6/2026).</t>
   </si>
   <si>
     <t xml:space="preserve">IF A CUTOFF IS MISSED</t>

--- a/accrued-commissions-analysis/Accrued_Commissions_Unclaimed_Property_Analysis.xlsx
+++ b/accrued-commissions-analysis/Accrued_Commissions_Unclaimed_Property_Analysis.xlsx
@@ -299,7 +299,7 @@
     <t xml:space="preserve">Columns R-S apply the dormancy tests to ALL unbooked items (upper bound). Columns T-W apply them only to the likely-commission and memo-flagged items. Even the T-W figures are upper bounds: within a larger check, only the agent's share (typically the check less the company's fee / split) is reportable; the company's share is revenue.</t>
   </si>
   <si>
-    <t xml:space="preserve">SHORT test = the state's period for wages / compensation for personal services. LONG test = the general catch-all period. Column X picks the likely test for each entity's default governing state now that agents are confirmed to be independent contractors (Texas and Florida: LONG; Illinois, Pennsylvania, Alabama: SHORT), and columns Y-Z apply it item by item, so an item whose owner state has been filled in uses its own state's test. See State Rules cols M-N for the basis. Management adopted these tests on 10/6/2026 after the statutes were verified; Texas applies the 3-year rule and the 1-year wage rule is not used.</t>
+    <t xml:space="preserve">SHORT test = the state's period for wages / compensation for personal services. LONG test = the general catch-all period. Column X applies the test management adopted on 10/6/2026 for each entity's default governing state, agents being independent contractors (Texas and Florida: LONG; Illinois, Pennsylvania, Alabama: SHORT), and columns Y-Z apply it item by item, so an item whose owner state has been filled in uses its own state's test. See State Rules cols M-N for the basis. Management adopted these tests on 10/6/2026 after the statutes were verified; Texas applies the 3-year rule and the 1-year wage rule is not used.</t>
   </si>
   <si>
     <t xml:space="preserve">Unknown agent = second priority rule. Per the Entity Management Database, URE Dallas, URE Houston, Quick Close Properties (TUR), URE Chicago and URE Philadelphia are all TEXAS LLCs; Gallery (RaySon Partners) is Florida; Leading Edge Realty is Alabama. Column B holds that formation state as each entity's DEFAULT governing state, so unknown-agent items at Chicago and Philly are tested under TEXAS rules (3-year general period for contractor commissions), not Illinois or Pennsylvania. When an agent's last-known address state is entered in Detail col U, that item switches to the address state's rules (first priority rule). Office state is shown in col AB for reference.</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">Current-month accrued (column D) is all September/October 2026 deposits in normal matching workflow. It is included so the total ties to the cash-requirements Summary, but none of it is near any dormancy period.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nothing here is legal advice. Dormancy periods, report dates, due-diligence rules, VDA terms and anti-limitation provisions on the State Rules tab were verified against the statute text and state treasury pages on 10/6/2026 (URLs in the Sources column). They state the rules; applying them to independent-contractor commissions and to the ICA forfeiture clauses is a judgment for counsel to confirm before filing.</t>
+    <t xml:space="preserve">Nothing here is legal advice. Dormancy periods, report dates, due-diligence rules, VDA terms and anti-limitation provisions on the State Rules tab were verified against the statute text and state treasury pages on 10/6/2026 (URLs in the Sources column). Management adopted the Texas 3-year test and decided not to rely on the ICA forfeiture clauses on 10/6/2026; counsel confirms the positions before the first filing.</t>
   </si>
   <si>
     <t xml:space="preserve">Unbooked deposited checks - item detail (prior-month accrued commissions block of each entity tab)</t>
@@ -1670,10 +1670,10 @@
     <t xml:space="preserve">RESOLVED: agents are independent contractors</t>
   </si>
   <si>
-    <t xml:space="preserve">User confirmed 10/6/2026. Verified 10/6/2026 from the statute text: Texas' 1-year rule applies to 'wages' as defined in Labor Code 61.001, which excludes independent contractors, and the Comptroller's property-code table puts commissions (MS02) at 3 years, so the 3-year general rule is the Texas test. Illinois, Pennsylvania and Alabama each reach 'other compensation for personal services', so their shorter periods apply. Florida's wage rule is not shown to reach contractors, so 5 years is likely. Counsel should confirm each.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm with counsel.</t>
+    <t xml:space="preserve">User confirmed 10/6/2026. Verified 10/6/2026 from the statute text: Texas' 1-year rule applies to 'wages' as defined in Labor Code 61.001, which excludes independent contractors, and the Comptroller's property-code table puts commissions (MS02) at 3 years, so the 3-year general rule is the Texas test. Illinois, Pennsylvania and Alabama each reach 'other compensation for personal services', so their shorter periods apply. Florida's wage rule does not reach contractors; a Florida holder with an unknown owner address uses 717.1035 (3 years), and 717.102 (5 years) where the owner has a Florida address. Positions adopted by management 10/6/2026; counsel confirms before the first filing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adopted 10/6/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">RESOLVED: no prior write-offs</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">1.K: an agent who collects a fee in their own name 'will forfeit any accrued but uncollected commissions'. 3.B: agent assigns commissions to TUR to secure indemnification. 5.F: breach of Section 5 (confidentiality / non-solicitation) means the agent 'shall lose all rights to any further commissions'. 8.C: amounts owed at or after termination may be deducted from commissions due.</t>
   </si>
   <si>
-    <t xml:space="preserve">Offset (8.C, 3.B) is a documented reduction. Forfeiture (1.K, 5.F) is a legal question: anti-limitation provisions in unclaimed property acts may override a contractual forfeiture. Do not rely on it without counsel and a documented breach.</t>
+    <t xml:space="preserve">Offset (8.C, 3.B) is a documented reduction. Forfeiture (1.K, 5.F) is not relied on against an escheat claim (decision 10/6/2026): Texas 74.308 disregards contract-based limits and 74.309 bars private escheat. It may be applied only to an item settled in the ordinary course before dormancy, with the breach documented.</t>
   </si>
   <si>
     <t xml:space="preserve">Policies item 6 Record Keeping</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">Post-termination commissions disbursed per the plan in effect, 'conditioned on Contractor having any and all dues, fees and expenses owing to Broker paid in full.' Broker may 'hold and/or apply any commissions owing to Contractor' to secure obligations. On termination, executed contracts split 70/30. 'If the Contractor's license expires or goes inactive, anything that is currently under contract brokerage split will be fifty/fifty. Contractor will have 30 days to bring their license back to active status. If Contractor fails to bring license back to active status within the 30 days, brokerage will keep 100% of commission.'</t>
   </si>
   <si>
-    <t xml:space="preserve">Offset rights as elsewhere, plus an express 100% retention clause for lapsed licenses. Whether Pennsylvania unclaimed property law honors a contractual retention against an escheat claim is for counsel.</t>
+    <t xml:space="preserve">Offset rights as elsewhere, plus an express 100% retention clause for lapsed licenses. Decision 10/6/2026: not relied on against an escheat claim; the Pennsylvania act is silent on contract-based bars and most Philly items default to Texas, where 74.308-74.309 apply.</t>
   </si>
   <si>
     <t xml:space="preserve">Para. 31 Fines and Penalties</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">'3. Any incomplete file(s) 30 days past closing will be paid at a 50/50 split. 4. Any incomplete file(s) 60 days past closing will be forfeited and grounds for termination.'</t>
   </si>
   <si>
-    <t xml:space="preserve">The most consequential clause for Philly's aged items: if a file was never completed, the ICA says the agent's share was forfeited at day 60 after closing. If counsel concludes Pennsylvania (or the agent's address state) honors this, those amounts are company revenue, not unclaimed property. Document the closing date and file status for each item before relying on it; anti-limitation provisions may override.</t>
+    <t xml:space="preserve">The most consequential clause for Philly's aged items: if a file was never completed, the ICA says the agent's share was forfeited at day 60 after closing. Decision 10/6/2026: the clause is not relied on against an escheat claim, so an aged Philly item is paid or reported at the agent's share whether or not the file was completed; the clause may be applied only to an item settled in the ordinary course before dormancy, with the day-60 file status documented.</t>
   </si>
   <si>
     <t xml:space="preserve">Para. 26 Contractor Information; Para. 28 Controlling Law; Para. 30 Paperless Pipeline</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">Treasury Voluntary Disclosure Agreement (searchandclaimpa.gov/docs/PA_Voluntary_Disclosure_Agreement.pdf): Treasury waives penalties and interest under 1301.24 and 1301.25 for property reported within the agreement; the holder must be coming forward voluntarily, not be under audit or self-audit, and not have had voluntary compliance in the past 10 years; 10-year look-back; report within 90 days of execution; no report may be filed before Treasury's signed approval. Without a VDA: interest of 12% per year from when the report was due (1301.24(b)) and a penalty of up to $1,000 per day (1301.24(c)); the Treasurer may waive for good cause and must waive penalties where the holder acted in good faith and without negligence (1301.25(c)). The prior draft's statement that PA's program ended in 2010 referred to a one-time amnesty and is superseded.</t>
   </si>
   <si>
-    <t xml:space="preserve">VERIFIED on 10/6/2026 from the statute text as published by PA Treasury (PA_UCP_Law.pdf: 1301.6, 1301.10, 1301.10a, 1301.11, 1301.13, 1301.16, 1301.24, 1301.25 read), the Treasury Dormancy Matrix, the Holder Reporting Handbook, the Reporting Guidelines page and the VDA form. The General Assembly's own viewer for 1929 Act 176 Art. XIII.1 (palegis.us) returned only its page shell and its PDF link returned an error, so the Treasury reprint is the text relied on. ANTI-LIMITATION: 1301.16 - expiration of any period specified by STATUTE OR COURT ORDER during which the owner could sue the holder does not prevent custody or affect the duty to report; unlike TX, IL, FL and AL it does NOT mention periods set by contract, and the Act contains no private-escheat prohibition equivalent to Tex. Prop. Code 74.309. The Philly ICA 60-day forfeiture clause is therefore not answered by the Pennsylvania statute either way; it is a contract-law question for counsel. Most Philly items default to Texas, where 74.308 and 74.309 apply.</t>
+    <t xml:space="preserve">VERIFIED on 10/6/2026 from the statute text as published by PA Treasury (PA_UCP_Law.pdf: 1301.6, 1301.10, 1301.10a, 1301.11, 1301.13, 1301.16, 1301.24, 1301.25 read), the Treasury Dormancy Matrix, the Holder Reporting Handbook, the Reporting Guidelines page and the VDA form. The General Assembly's own viewer for 1929 Act 176 Art. XIII.1 (palegis.us) returned only its page shell and its PDF link returned an error, so the Treasury reprint is the text relied on. ANTI-LIMITATION: 1301.16 - expiration of any period specified by STATUTE OR COURT ORDER during which the owner could sue the holder does not prevent custody or affect the duty to report; unlike TX, IL, FL and AL it does NOT mention periods set by contract, and the Act contains no private-escheat prohibition equivalent to Tex. Prop. Code 74.309. The Philly ICA 60-day forfeiture clause is therefore not answered by the Pennsylvania statute either way; management decided on 10/6/2026 not to rely on it against an escheat claim. Most Philly items default to Texas, where 74.308 and 74.309 apply.</t>
   </si>
   <si>
     <t xml:space="preserve">1301.10(2) reaches 'wages or other compensation for personal services', and Treasury's handbook, matrix and VDA form all describe the 2-year exception as covering commissions. 3-year rule (1301.10(1)) is the fallback. Verified from the statute text.</t>
